--- a/dashboard-ui/src/components/Research/variables/Variable Definitions TCCC.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions TCCC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Projects\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EE4253-4697-4C50-BC41-F78AEF5668B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72503F9-BC13-4F47-9A95-63EE6295D9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B335D1ED-2780-4984-A298-197D94347E3F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="89">
   <si>
     <t>Field Name</t>
   </si>
@@ -160,12 +160,6 @@
     <t>Proportion of tags where participant placed a patient in dead/expectant incorrectly</t>
   </si>
   <si>
-    <t>Total time in seconds the participant spent performing hemorrhage control across all patients</t>
-  </si>
-  <si>
-    <t>Total number of mistakes made during the simulation</t>
-  </si>
-  <si>
     <t>Percentage score of correct treatments applied out of total tools used plus missed required treatments; (correct tools / (total tools + missed)) * 100</t>
   </si>
   <si>
@@ -262,9 +256,6 @@
     <t>Decimal (seconds)</t>
   </si>
   <si>
-    <t>Numeric (seconds) or '-' if not treated</t>
-  </si>
-  <si>
     <t>Decimal 0.0 - 1.0</t>
   </si>
   <si>
@@ -280,9 +271,6 @@
     <t>Numeric (seconds)</t>
   </si>
   <si>
-    <t>Total hemorrhage control time if performed</t>
-  </si>
-  <si>
     <t>Integer 1+</t>
   </si>
   <si>
@@ -293,6 +281,12 @@
   </si>
   <si>
     <t>1st - {N}th Patient</t>
+  </si>
+  <si>
+    <t>Total number of combined tagging_errors + missed_hemorrhage + incorrect treatments</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> time from scene start until all required HC treatments completed; only has a value when flag = 1</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1159,7 @@
     <col min="7" max="7" width="64.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="71.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="81.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="47" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="75.08984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="126.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="84.90625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="61.453125" bestFit="1" customWidth="1"/>
@@ -1278,7 +1272,7 @@
         <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AD1" t="s">
         <v>28</v>
@@ -1426,183 +1420,183 @@
         <v>45</v>
       </c>
       <c r="I3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" t="s">
         <v>46</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>47</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>48</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>49</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>50</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3" t="s">
         <v>51</v>
       </c>
-      <c r="O3" t="s">
+      <c r="R3" t="s">
         <v>52</v>
       </c>
-      <c r="P3" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="S3" t="s">
         <v>53</v>
       </c>
-      <c r="R3" t="s">
+      <c r="T3" t="s">
         <v>54</v>
       </c>
-      <c r="S3" t="s">
+      <c r="U3" t="s">
         <v>55</v>
       </c>
-      <c r="T3" t="s">
+      <c r="V3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W3" t="s">
         <v>56</v>
       </c>
-      <c r="U3" t="s">
+      <c r="X3" t="s">
         <v>57</v>
       </c>
-      <c r="V3" t="s">
-        <v>86</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z3" t="s">
         <v>58</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AA3" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="AB3" t="s">
         <v>60</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>61</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3" t="s">
         <v>62</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AE3" t="s">
         <v>63</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AF3" t="s">
         <v>64</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AG3" t="s">
         <v>65</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AH3" t="s">
         <v>66</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" t="s">
+      <c r="I4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J4" t="s">
         <v>71</v>
       </c>
-      <c r="E4" t="s">
+      <c r="K4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+      <c r="O4" t="s">
+        <v>72</v>
+      </c>
+      <c r="P4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>73</v>
+      </c>
+      <c r="R4" t="s">
         <v>81</v>
       </c>
-      <c r="F4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="S4" t="s">
+        <v>78</v>
+      </c>
+      <c r="T4" t="s">
+        <v>74</v>
+      </c>
+      <c r="U4" t="s">
+        <v>75</v>
+      </c>
+      <c r="V4" t="s">
         <v>82</v>
       </c>
-      <c r="L4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="W4" t="s">
+        <v>82</v>
+      </c>
+      <c r="X4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y4" t="s">
         <v>74</v>
       </c>
-      <c r="N4" t="s">
-        <v>73</v>
-      </c>
-      <c r="O4" t="s">
-        <v>74</v>
-      </c>
-      <c r="P4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>75</v>
-      </c>
-      <c r="R4" t="s">
-        <v>84</v>
-      </c>
-      <c r="S4" t="s">
-        <v>81</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="Z4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC4" t="s">
         <v>76</v>
       </c>
-      <c r="U4" t="s">
+      <c r="AD4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF4" t="s">
         <v>77</v>
       </c>
-      <c r="V4" t="s">
-        <v>85</v>
-      </c>
-      <c r="W4" t="s">
-        <v>85</v>
-      </c>
-      <c r="X4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>79</v>
-      </c>
       <c r="AG4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions TCCC.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions TCCC.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Projects\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72503F9-BC13-4F47-9A95-63EE6295D9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{72B709A4-92EF-4A27-A6F8-54CA82AAD129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B335D1ED-2780-4984-A298-197D94347E3F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C225C15C-1D6D-4CFE-A0FB-ABC62FC30937}"/>
   </bookViews>
   <sheets>
-    <sheet name="tccc_field_definitions" sheetId="1" r:id="rId1"/>
+    <sheet name="Variable Definitions TCCC" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="86">
   <si>
     <t>Field Name</t>
   </si>
@@ -85,9 +85,6 @@
     <t>TCCC Hemorrhage control</t>
   </si>
   <si>
-    <t>TCCC Hemorrhage control_time</t>
-  </si>
-  <si>
     <t>{Patient} Time</t>
   </si>
   <si>
@@ -106,6 +103,9 @@
     <t>{Patient} Tag</t>
   </si>
   <si>
+    <t>1st - {N}th Patient</t>
+  </si>
+  <si>
     <t>{Patient} Time (s)</t>
   </si>
   <si>
@@ -142,10 +142,7 @@
     <t>9-digit participant ID derived from the filename</t>
   </si>
   <si>
-    <t>Elapsed time in seconds from session start until the participant began triaging patients</t>
-  </si>
-  <si>
-    <t>Total number of triage tags applied by the participant across all patients</t>
+    <t>Number of distinct patients the participant tagged (the last tag applied to each patient is the one counted)</t>
   </si>
   <si>
     <t>Proportion of tags that matched the correct triage color for each patient</t>
@@ -160,13 +157,13 @@
     <t>Proportion of tags where participant placed a patient in dead/expectant incorrectly</t>
   </si>
   <si>
-    <t>Percentage score of correct treatments applied out of total tools used plus missed required treatments; (correct tools / (total tools + missed)) * 100</t>
-  </si>
-  <si>
-    <t>Total number of assessment actions performed (SpO2 pulse breathing checks) across all patients</t>
-  </si>
-  <si>
-    <t>Average number of assessment actions performed per patient engaged</t>
+    <t>Total number of combined tagging_errors + missed_hemorrhage + incorrect treatments</t>
+  </si>
+  <si>
+    <t>Number of assessment actions (SpO2/pulse/breathing) across all patients; repeats of the same check type within 5 seconds are not counted again</t>
+  </si>
+  <si>
+    <t>Average number of assessment actions per patient engaged (same-type checks within 5 seconds are de-duplicated)</t>
   </si>
   <si>
     <t>Total number of treatment tools applied across all patients (excluding pulse oximeter)</t>
@@ -175,19 +172,19 @@
     <t>Average number of treatment tools applied per patient treated</t>
   </si>
   <si>
+    <t>Same as Time to Triage Scene; total session duration from session start to the final action before session end</t>
+  </si>
+  <si>
     <t>Average triage time divided by number of patients engaged</t>
   </si>
   <si>
-    <t>Average number of times the participant re-engaged each patient</t>
-  </si>
-  <si>
     <t>Proportion of triage tags that were correct</t>
   </si>
   <si>
     <t>Whether the participant correctly tagged at least one expectant patient as black</t>
   </si>
   <si>
-    <t>Whether the participant performed any hemorrhage control</t>
+    <t>Whether the participant completed all required hemorrhage control (1 only when every required HC procedure is completed)</t>
   </si>
   <si>
     <t>Total time in seconds the participant spent interacting with this specific patient</t>
@@ -196,13 +193,16 @@
     <t>The order in which the participant first engaged this patient</t>
   </si>
   <si>
-    <t>Number of assessment actions performed on this specific patient</t>
+    <t>Whether the participant chose to evacuate this patient</t>
+  </si>
+  <si>
+    <t>Number of assessment actions performed on this specific patient (same-type checks within 5 seconds are de-duplicated)</t>
   </si>
   <si>
     <t>Number of treatment tools applied to this specific patient</t>
   </si>
   <si>
-    <t>Triage tag color the participant assigned to this patient</t>
+    <t>Triage tag color the participant assigned to this patient (raw value; may also appear as yellow_orange / green_blue / gray)</t>
   </si>
   <si>
     <t>Whether the tag applied to the Nth patient in order was correct</t>
@@ -232,7 +232,7 @@
     <t>Integer; 0 to number of patients in scenario</t>
   </si>
   <si>
-    <t>Decimal 0.0 â€“ 1.0</t>
+    <t>Decimal 0.0 - 1.0</t>
   </si>
   <si>
     <t>Integer; 0+</t>
@@ -244,49 +244,40 @@
     <t>Decimal (seconds); 0.0+</t>
   </si>
   <si>
+    <t>Decimal 0.0+</t>
+  </si>
+  <si>
     <t>Yes / No</t>
   </si>
   <si>
     <t>0 (no) / 1 (yes)</t>
   </si>
   <si>
+    <t>Numeric (seconds)</t>
+  </si>
+  <si>
+    <t>Integer 1+</t>
+  </si>
+  <si>
+    <t>red / yellow / green / black (raw values may also include yellow_orange / green_blue / gray)</t>
+  </si>
+  <si>
     <t>0 (incorrect) / 1 (correct)</t>
   </si>
   <si>
     <t>Decimal (seconds)</t>
   </si>
   <si>
-    <t>Decimal 0.0 - 1.0</t>
-  </si>
-  <si>
-    <t>0.0 - 100.0</t>
-  </si>
-  <si>
-    <t>Same as Time to Triage Scene, total time to begin triaging</t>
-  </si>
-  <si>
-    <t>Decimal 0.0+</t>
-  </si>
-  <si>
-    <t>Numeric (seconds)</t>
-  </si>
-  <si>
-    <t>Integer 1+</t>
-  </si>
-  <si>
-    <t>Whether the participant chose to evacuate this patient</t>
-  </si>
-  <si>
-    <t>red / yellow / green / black</t>
-  </si>
-  <si>
-    <t>1st - {N}th Patient</t>
-  </si>
-  <si>
-    <t>Total number of combined tagging_errors + missed_hemorrhage + incorrect treatments</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> time from scene start until all required HC treatments completed; only has a value when flag = 1</t>
+    <t>Percentage score of correct treatments applied out of total tools used plus missed required treatments; (correct tools / (total tools + missed))</t>
+  </si>
+  <si>
+    <t>Elapsed time in seconds from session start  to the final action before session end; i.e. total scene/session duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> time from scene start until all required HC treatments completed; only has a value when TCCC Hemorrhage control = 1</t>
+  </si>
+  <si>
+    <t>Average number of engagement visits per patient — the first visit counts as 1 and each return visit adds 1, the value is 1.0 when no patient is revisited and higher when patients are revisited</t>
   </si>
 </sst>
 </file>
@@ -1146,47 +1137,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64312BC-F3F9-4479-ABDB-C040E1EA11E7}">
-  <dimension ref="A1:AH4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9022F6AF-1660-4719-ACB9-EC9BE9EB9D68}">
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="75.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="62.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="114.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61.90625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="65.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="64.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="71.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="81.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="75.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="101.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="75.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="126.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="84.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="61.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="126.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="100.1796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="74.7265625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="53.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="94.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="50.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="161" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="36.36328125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="68.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="51.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="56.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="68.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="51.36328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="65.453125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="57.08984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="49.90625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="47.7265625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="54" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="65.7265625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="44.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="54.54296875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="63.26953125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="62.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="106.90625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="68.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="51.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="47" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="105.26953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="49.90625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="105.08984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="54" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="65.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="44.453125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="54.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="63.26953125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="62.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1272,25 +1262,22 @@
         <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="AD1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1373,10 +1360,10 @@
         <v>34</v>
       </c>
       <c r="AB2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AD2" t="s">
         <v>36</v>
@@ -1385,16 +1372,13 @@
         <v>36</v>
       </c>
       <c r="AF2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG2" t="s">
         <v>37</v>
       </c>
-      <c r="AH2" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1402,64 +1386,64 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" t="s">
         <v>40</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>41</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>42</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>43</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>44</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s">
         <v>45</v>
       </c>
-      <c r="I3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" t="s">
-        <v>87</v>
-      </c>
       <c r="K3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" t="s">
         <v>46</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>47</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>48</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>49</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>50</v>
-      </c>
-      <c r="P3" t="s">
-        <v>80</v>
       </c>
       <c r="Q3" t="s">
         <v>51</v>
       </c>
       <c r="R3" t="s">
+        <v>85</v>
+      </c>
+      <c r="S3" t="s">
         <v>52</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>53</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>54</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>55</v>
-      </c>
-      <c r="V3" t="s">
-        <v>88</v>
       </c>
       <c r="W3" t="s">
         <v>56</v>
@@ -1468,37 +1452,34 @@
         <v>57</v>
       </c>
       <c r="Y3" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="Z3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AC3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AD3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AE3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AF3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AG3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1509,13 +1490,13 @@
         <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H4" t="s">
         <v>70</v>
@@ -1527,7 +1508,7 @@
         <v>71</v>
       </c>
       <c r="K4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="L4" t="s">
         <v>71</v>
@@ -1548,55 +1529,52 @@
         <v>73</v>
       </c>
       <c r="R4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="S4" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" t="s">
+        <v>75</v>
+      </c>
+      <c r="U4" t="s">
+        <v>76</v>
+      </c>
+      <c r="V4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W4" t="s">
         <v>78</v>
       </c>
-      <c r="T4" t="s">
-        <v>74</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="X4" t="s">
         <v>75</v>
       </c>
-      <c r="V4" t="s">
-        <v>82</v>
-      </c>
-      <c r="W4" t="s">
-        <v>82</v>
-      </c>
-      <c r="X4" t="s">
-        <v>83</v>
-      </c>
       <c r="Y4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z4" t="s">
         <v>71</v>
       </c>
       <c r="AA4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD4" t="s">
         <v>71</v>
       </c>
-      <c r="AB4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>82</v>
-      </c>
       <c r="AE4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AF4" t="s">
         <v>77</v>
       </c>
       <c r="AG4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions TCCC.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions TCCC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{72B709A4-92EF-4A27-A6F8-54CA82AAD129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213838A7-30FB-4DC2-B968-06D482EA9101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C225C15C-1D6D-4CFE-A0FB-ABC62FC30937}"/>
   </bookViews>
@@ -268,9 +268,6 @@
     <t>Decimal (seconds)</t>
   </si>
   <si>
-    <t>Percentage score of correct treatments applied out of total tools used plus missed required treatments; (correct tools / (total tools + missed))</t>
-  </si>
-  <si>
     <t>Elapsed time in seconds from session start  to the final action before session end; i.e. total scene/session duration</t>
   </si>
   <si>
@@ -278,6 +275,9 @@
   </si>
   <si>
     <t>Average number of engagement visits per patient — the first visit counts as 1 and each return visit adds 1, the value is 1.0 when no patient is revisited and higher when patients are revisited</t>
+  </si>
+  <si>
+    <t>Decimal score of correct treatments applied out of total tools used plus missed required treatments; (correct tools / (total tools + missed))</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1386,7 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
         <v>40</v>
@@ -1404,13 +1404,13 @@
         <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s">
         <v>45</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -1431,7 +1431,7 @@
         <v>51</v>
       </c>
       <c r="R3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S3" t="s">
         <v>52</v>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions TCCC.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions TCCC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Projects\itm-evaluation-dashboard\dashboard-ui\src\components\Research\variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213838A7-30FB-4DC2-B968-06D482EA9101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB26DC10-0011-4022-8349-112D34D0C94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C225C15C-1D6D-4CFE-A0FB-ABC62FC30937}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="94">
   <si>
     <t>Field Name</t>
   </si>
@@ -278,6 +278,30 @@
   </si>
   <si>
     <t>Decimal score of correct treatments applied out of total tools used plus missed required treatments; (correct tools / (total tools + missed))</t>
+  </si>
+  <si>
+    <t>Estimated Evac Decision Time Confidence</t>
+  </si>
+  <si>
+    <t>High / Medium / Low</t>
+  </si>
+  <si>
+    <t>Estimated Evac Decision Time</t>
+  </si>
+  <si>
+    <t>In these medical training scenarios, participants treat casualties and are then asked which ones to send out for evacuation. This is roughly how long they took to make that choice. It's an estimate, because older sessions didn't record the exact moment they were asked.</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>Evac_decision_time</t>
+  </si>
+  <si>
+    <t>How long the participant took to choose which casualties to evacuate, measured from when the evacuation request appeared to when they locked in their choice. Recorded directly for June 2026 sessions onward.</t>
+  </si>
+  <si>
+    <t>How much to trust the Estimated Evac Decision Time. High means we're fairly sure it's accurate; Low means it's a rougher guess.</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9022F6AF-1660-4719-ACB9-EC9BE9EB9D68}">
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
@@ -1168,15 +1192,17 @@
     <col min="25" max="25" width="105.26953125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="49.90625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="105.08984375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="54" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="65.7265625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="44.453125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="54.54296875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="63.26953125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="62.26953125" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="105.08984375" customWidth="1"/>
+    <col min="30" max="30" width="54" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="65.7265625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="44.453125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="54.54296875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="63.26953125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="62.26953125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1259,25 +1285,34 @@
         <v>26</v>
       </c>
       <c r="AB1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>32</v>
       </c>
+      <c r="AJ1" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1360,25 +1395,34 @@
         <v>34</v>
       </c>
       <c r="AB2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD2" t="s">
         <v>35</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>36</v>
       </c>
       <c r="AE2" t="s">
         <v>36</v>
       </c>
       <c r="AF2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH2" t="s">
         <v>37</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>37</v>
       </c>
+      <c r="AJ2" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1461,25 +1505,34 @@
         <v>60</v>
       </c>
       <c r="AB3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD3" t="s">
         <v>61</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AE3" t="s">
         <v>62</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AF3" t="s">
         <v>63</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AG3" t="s">
         <v>64</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AH3" t="s">
         <v>65</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AI3" t="s">
         <v>66</v>
       </c>
+      <c r="AJ3" t="s">
+        <v>92</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1559,22 +1612,31 @@
         <v>79</v>
       </c>
       <c r="AB4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD4" t="s">
         <v>80</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AE4" t="s">
         <v>77</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
         <v>71</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>77</v>
       </c>
       <c r="AG4" t="s">
         <v>81</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
